--- a/inst/extdata/ex01/User_10102018.xlsx
+++ b/inst/extdata/ex01/User_10102018.xlsx
@@ -5,7 +5,7 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Profils\mcanouil\Downloads\DATA\endoc_beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Profils\mcanouil\Downloads\DATA\endoc_beta\ex01\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -49,12 +49,6 @@
     <t>BLANK</t>
   </si>
   <si>
-    <t>SN1</t>
-  </si>
-  <si>
-    <t>SN2</t>
-  </si>
-  <si>
     <t>Sample</t>
   </si>
   <si>
@@ -89,9 +83,6 @@
   </si>
   <si>
     <t>Concentration (µg/L)</t>
-  </si>
-  <si>
-    <t>LYSAT</t>
   </si>
   <si>
     <t>Target</t>
@@ -134,6 +125,15 @@
   </si>
   <si>
     <t>0.5 mM Glc + A</t>
+  </si>
+  <si>
+    <t>LYSATE</t>
+  </si>
+  <si>
+    <t>SUPERNATANT1</t>
+  </si>
+  <si>
+    <t>SUPERNATANT2</t>
   </si>
 </sst>
 </file>
@@ -2920,13 +2920,13 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>1</v>
@@ -2935,19 +2935,19 @@
         <v>0</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N1" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -2955,10 +2955,10 @@
         <v>43383</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
@@ -3210,22 +3210,22 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>1</v>
@@ -3234,19 +3234,19 @@
         <v>0</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -3267,16 +3267,16 @@
         <v>siNTP</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1">
         <v>0.22417039999999999</v>
@@ -3319,16 +3319,16 @@
         <v>siNTP</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1">
         <v>0.22104550000000001</v>
@@ -3371,16 +3371,16 @@
         <v>siNTP</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1">
         <v>0.22085260000000001</v>
@@ -3423,16 +3423,16 @@
         <v>siNTP</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I5" s="1">
         <v>0.33171919999999999</v>
@@ -3475,16 +3475,16 @@
         <v>siNTP</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I6" s="1">
         <v>0.33739239999999998</v>
@@ -3527,16 +3527,16 @@
         <v>siNTP</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I7" s="1">
         <v>0.37622100000000003</v>
@@ -3579,16 +3579,16 @@
         <v>siNTP</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I8">
         <v>0.39833659999999999</v>
@@ -3633,16 +3633,16 @@
         <v>siNTP</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>0.2715764</v>
@@ -3687,16 +3687,16 @@
         <v>siNTP</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I10">
         <v>0.3177606</v>
@@ -3741,16 +3741,16 @@
         <v>siNTP</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I11">
         <v>0.28898210000000002</v>
@@ -3795,16 +3795,16 @@
         <v>siNTP</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I12">
         <v>0.3648556</v>
@@ -3849,16 +3849,16 @@
         <v>siNTP</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I13">
         <v>0.46582079999999998</v>
@@ -3903,16 +3903,16 @@
         <v>siNTP</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="H14" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I14" s="1">
         <v>0.23270979999999999</v>
@@ -3957,16 +3957,16 @@
         <v>siNTP</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="H15" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I15" s="1">
         <v>0.21746770000000001</v>
@@ -4011,16 +4011,16 @@
         <v>siNTP</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I16" s="1">
         <v>0.27606730000000002</v>
@@ -4065,16 +4065,16 @@
         <v>siNTP</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I17" s="1">
         <v>0.59939379999999998</v>
@@ -4119,16 +4119,16 @@
         <v>siNTP</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I18" s="1">
         <v>0.67264279999999999</v>
@@ -4173,16 +4173,16 @@
         <v>siNTP</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I19" s="1">
         <v>0.71760619999999997</v>
@@ -4221,10 +4221,9 @@
   <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="0" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="0" hidden="1" customWidth="1"/>
-    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="1" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
@@ -4242,22 +4241,22 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>1</v>
@@ -4266,19 +4265,19 @@
         <v>0</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -4299,16 +4298,16 @@
         <v>siGENE</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1">
         <v>0.45181329999999997</v>
@@ -4351,16 +4350,16 @@
         <v>siGENE</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1">
         <v>0.31413999999999997</v>
@@ -4403,16 +4402,16 @@
         <v>siGENE</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1">
         <v>0.29734709999999998</v>
@@ -4455,16 +4454,16 @@
         <v>siGENE</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I5" s="1">
         <v>0.31359559999999997</v>
@@ -4507,16 +4506,16 @@
         <v>siGENE</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I6" s="1">
         <v>0.28795500000000002</v>
@@ -4559,16 +4558,16 @@
         <v>siGENE</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I7" s="1">
         <v>0.3430319</v>
@@ -4611,16 +4610,16 @@
         <v>siGENE</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I8">
         <v>0.24077100000000001</v>
@@ -4665,16 +4664,16 @@
         <v>siGENE</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>0.19412489999999999</v>
@@ -4719,16 +4718,16 @@
         <v>siGENE</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I10">
         <v>0.23539879999999999</v>
@@ -4773,16 +4772,16 @@
         <v>siGENE</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I11">
         <v>0.28282059999999998</v>
@@ -4827,16 +4826,16 @@
         <v>siGENE</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I12">
         <v>0.30227989999999999</v>
@@ -4881,16 +4880,16 @@
         <v>siGENE</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I13">
         <v>0.31732539999999998</v>
@@ -4935,16 +4934,16 @@
         <v>siGENE</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I14" s="1">
         <v>0.39352399999999998</v>
@@ -4989,16 +4988,16 @@
         <v>siGENE</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I15" s="1">
         <v>0.29944229999999999</v>
@@ -5043,16 +5042,16 @@
         <v>siGENE</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I16" s="1">
         <v>0.3549486</v>
@@ -5097,16 +5096,16 @@
         <v>siGENE</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I17" s="1">
         <v>0.77992479999999997</v>
@@ -5151,16 +5150,16 @@
         <v>siGENE</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I18" s="1">
         <v>0.62352810000000003</v>
@@ -5205,16 +5204,16 @@
         <v>siGENE</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I19" s="1">
         <v>0.68339159999999999</v>
